--- a/data/trans_orig/P32E$bar_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P32E$bar_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los lugares donde se realiza el consumo de alcohol (atracón) (multirrespuesta) en 2023</t>
+          <t>Población según los lugares donde se realiza el consumo de alcohol (atracón) (multirrespuesta) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6970</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16459</t>
+          <t>16552</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>10378</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20796</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,8%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12124</t>
+          <t>11979</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21916</t>
+          <t>21611</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>447</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13972</t>
+          <t>14160</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24018</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,9%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t>9769</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9964</t>
+          <t>9514</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12846</t>
+          <t>13168</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13578</t>
+          <t>14099</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>43,97%</t>
         </is>
       </c>
     </row>
@@ -1182,97 +1182,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1520</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1033</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>20,75%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1459</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56633</t>
+          <t>57223</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>75307</t>
+          <t>76952</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11153</t>
+          <t>11566</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18884</t>
+          <t>18956</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>72528</t>
+          <t>71468</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>92383</t>
+          <t>92784</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>81,01%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31910</t>
+          <t>30776</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53373</t>
+          <t>52095</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12239</t>
+          <t>12406</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39073</t>
+          <t>39151</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61230</t>
+          <t>61710</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,88%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14521</t>
+          <t>14072</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35558</t>
+          <t>32702</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17117</t>
+          <t>18545</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39179</t>
+          <t>40120</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>35,03%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10238</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29075</t>
+          <t>27225</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>606</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>6339</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>11677</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31066</t>
+          <t>29313</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11651</t>
+          <t>11828</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>21238</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>14292</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24662</t>
+          <t>24418</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29249</t>
+          <t>29760</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43249</t>
+          <t>43635</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,85%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10421</t>
+          <t>10745</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19885</t>
+          <t>20097</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14083</t>
+          <t>14937</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>16805</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>32311</t>
+          <t>31216</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>60,7%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>12202</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12659</t>
+          <t>13599</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21175</t>
+          <t>21114</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,06%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>13012</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17090</t>
+          <t>18823</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7246</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9128</t>
+          <t>10597</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13279</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83144</t>
+          <t>82656</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107201</t>
+          <t>106927</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32260</t>
+          <t>32959</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45441</t>
+          <t>45558</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>122047</t>
+          <t>122013</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>149697</t>
+          <t>149368</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,43%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63028</t>
+          <t>62610</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88466</t>
+          <t>88798</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26168</t>
+          <t>26266</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78345</t>
+          <t>78738</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>107445</t>
+          <t>108303</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,69%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23035</t>
+          <t>23340</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46999</t>
+          <t>47246</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18847</t>
+          <t>19003</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>33296</t>
+          <t>32805</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>58602</t>
+          <t>59452</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18051</t>
+          <t>17908</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39551</t>
+          <t>40762</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17527</t>
+          <t>18054</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26016</t>
+          <t>25103</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50504</t>
+          <t>49650</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>849</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8513</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>11857</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15977</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32E$bar_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P32E$bar_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6970</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16552</t>
+          <t>18110</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>714</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15269</t>
+          <t>16347</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>10894</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>63,45%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>19208</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11979</t>
+          <t>13208</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21611</t>
+          <t>23414</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>541</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>19567</t>
+          <t>21835</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14160</t>
+          <t>16237</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>26593</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,99%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>9621</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9514</t>
+          <t>10174</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7591</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>612</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14099</t>
+          <t>14388</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>41,12%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67277</t>
+          <t>75673</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57223</t>
+          <t>64538</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76952</t>
+          <t>85432</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15820</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>14924</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18956</t>
+          <t>24642</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>83097</t>
+          <t>95796</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>71468</t>
+          <t>83654</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>92784</t>
+          <t>106771</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>79,33%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>42010</t>
+          <t>50526</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30776</t>
+          <t>38721</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52095</t>
+          <t>62745</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12406</t>
+          <t>16008</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>49793</t>
+          <t>60727</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39151</t>
+          <t>49328</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61710</t>
+          <t>73678</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,74%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22561</t>
+          <t>26644</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14072</t>
+          <t>16110</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32702</t>
+          <t>39717</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4462</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>13831</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>27023</t>
+          <t>33780</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18545</t>
+          <t>21899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40120</t>
+          <t>47233</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,09%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>18125</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9421</t>
+          <t>10558</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27225</t>
+          <t>30417</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>623</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6339</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>19659</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11677</t>
+          <t>12040</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29313</t>
+          <t>32070</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>944</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>6468</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>17728</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>11534</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21238</t>
+          <t>21999</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20840</t>
+          <t>21805</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14292</t>
+          <t>14602</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24418</t>
+          <t>25195</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>37648</t>
+          <t>39533</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29760</t>
+          <t>30679</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43635</t>
+          <t>45377</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>83,27%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15436</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10745</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20097</t>
+          <t>21305</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>9876</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14937</t>
+          <t>15546</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>24216</t>
+          <t>26370</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>18516</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>31216</t>
+          <t>34680</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>63,64%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12202</t>
+          <t>13473</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13599</t>
+          <t>14027</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>14157</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21114</t>
+          <t>23193</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13012</t>
+          <t>14047</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9221</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18823</t>
+          <t>19202</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>35,24%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10597</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6157</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2255</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13789</t>
+          <t>13211</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>95952</t>
+          <t>106085</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>82656</t>
+          <t>92142</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>106927</t>
+          <t>118944</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40062</t>
+          <t>45591</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32959</t>
+          <t>38081</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45558</t>
+          <t>51984</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>136014</t>
+          <t>151676</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>122013</t>
+          <t>134982</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>149368</t>
+          <t>166030</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>74,09%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>74985</t>
+          <t>86227</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62610</t>
+          <t>72984</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88798</t>
+          <t>99464</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26266</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>93576</t>
+          <t>108932</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78738</t>
+          <t>93370</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>108303</t>
+          <t>124807</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>55,7%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33436</t>
+          <t>38147</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23340</t>
+          <t>25640</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47246</t>
+          <t>52483</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19003</t>
+          <t>22969</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>45169</t>
+          <t>52929</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>32805</t>
+          <t>40183</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>59452</t>
+          <t>70107</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>31,29%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>18420</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40762</t>
+          <t>41677</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18054</t>
+          <t>18175</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>37014</t>
+          <t>38264</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25103</t>
+          <t>27078</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49650</t>
+          <t>53476</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>935</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1633</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11857</t>
+          <t>12407</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
